--- a/output/pdf_financials_xlsx/TK.xlsx
+++ b/output/pdf_financials_xlsx/TK.xlsx
@@ -5702,49 +5702,49 @@
         <v>0.799524</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>1.050477</v>
+        <v>1.063937</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>1.234833</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.153851</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.275237</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.834525</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.363949</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.457243</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.198982</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.51835</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>6.062126</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>7.176618</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>7.778618</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>7.813618</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>7.813618</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>7.881726</v>
       </c>
     </row>
     <row r="93">
@@ -7096,7 +7096,7 @@
         <v>-0.830224</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.733903</v>
+        <v>-2.285132</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>-4.499571</v>
@@ -9302,7 +9302,11 @@
           <t>Share-based payments reserve 6</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -10118,7 +10122,11 @@
           <t>Share-based payments reserve 7</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -11054,7 +11062,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -16906,7 +16918,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TK.xlsx
+++ b/output/pdf_financials_xlsx/TK.xlsx
@@ -999,52 +999,52 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002363</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.0007159999999999999</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.008233000000000001</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.023037</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.016837</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.023267</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.053214</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.033422</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.087281</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.195329</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.236633</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.099735</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.141138</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.524057</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.240121</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.079232</v>
       </c>
     </row>
     <row r="13">
@@ -1984,52 +1984,52 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.014553</v>
+        <v>-1.016916</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.562708</v>
+        <v>-0.563424</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.7803870000000001</v>
+        <v>-0.78862</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.695336</v>
+        <v>-2.718373</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.655446</v>
+        <v>-2.672283</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.804971</v>
+        <v>-3.828238</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.690714</v>
+        <v>-1.743928</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.710869</v>
+        <v>-1.744291</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.188838</v>
+        <v>-3.276119</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.816365</v>
+        <v>-3.011694</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.446002</v>
+        <v>-2.682635</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.054644</v>
+        <v>-2.154379</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.916447</v>
+        <v>-1.057585</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.464333</v>
+        <v>-1.98839</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.222863</v>
+        <v>-1.462984</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.069572</v>
+        <v>-1.148804</v>
       </c>
     </row>
     <row r="28">
@@ -2094,52 +2094,52 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.014553</v>
+        <v>-1.016916</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.562708</v>
+        <v>-0.563424</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.7803870000000001</v>
+        <v>-0.78862</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.693795</v>
+        <v>-2.716832</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.654469</v>
+        <v>-2.671306</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.801836</v>
+        <v>-3.825103</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.680097</v>
+        <v>-1.733311</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.702972</v>
+        <v>-1.736394</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.18254</v>
+        <v>-3.269821</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.810429</v>
+        <v>-3.005758</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.443012</v>
+        <v>-2.679645</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.05411</v>
+        <v>-2.153845</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.916447</v>
+        <v>-1.057585</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.464333</v>
+        <v>-1.98839</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.222863</v>
+        <v>-1.462984</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.069572</v>
+        <v>-1.148804</v>
       </c>
     </row>
     <row r="30">
@@ -2385,37 +2385,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.07510600000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.884144</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.475807</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.220006</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.65341</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>5.838547</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>6.912872</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.765069</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>6.036919</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>14.260023</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>6.861443</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>4.041734</v>
@@ -2427,10 +2427,10 @@
         <v>7.484845</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>2.076217</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>6.431318</v>
       </c>
     </row>
     <row r="35">
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.07510600000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.884144</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.475807</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.220006</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.65341</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>5.838547</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>6.912872</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.765069</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>6.036919</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>14.260023</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>6.861443</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>4.041734</v>
@@ -2537,10 +2537,10 @@
         <v>7.484845</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>2.076217</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>6.431318</v>
       </c>
     </row>
     <row r="37">
@@ -3155,37 +3155,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.162086</v>
+        <v>2.08698</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.898898</v>
+        <v>0.014754</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.521418</v>
+        <v>0.045611</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.247278</v>
+        <v>0.027272</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.687388</v>
+        <v>0.033978</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>5.867961</v>
+        <v>0.029414</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.957643</v>
+        <v>0.044771</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.826165</v>
+        <v>0.061096</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>6.137879</v>
+        <v>0.10096</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>14.326375</v>
+        <v>0.06635199999999999</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>6.981321</v>
+        <v>0.119878</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>7.732459</v>
@@ -3197,10 +3197,10 @@
         <v>0.084811</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.212047</v>
+        <v>0.13583</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>6.52199</v>
+        <v>0.090672</v>
       </c>
     </row>
     <row r="49">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -29926,7 +29926,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E241" s="5" t="n">

--- a/output/pdf_financials_xlsx/TK.xlsx
+++ b/output/pdf_financials_xlsx/TK.xlsx
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.002105</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0.001541</v>
@@ -2100,7 +2100,7 @@
         <v>-0.563424</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.78862</v>
+        <v>-0.786515</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.716832</v>
@@ -6103,10 +6103,10 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.002105</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.001541</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -6769,7 +6769,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.012795</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -16632,7 +16632,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -17110,7 +17114,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -27750,7 +27758,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TK.xlsx
+++ b/output/pdf_financials_xlsx/TK.xlsx
@@ -6161,43 +6161,43 @@
         <v>-0.034576</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0.00527</v>
+        <v>0.029506</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>-0.00178</v>
+        <v>0.003245</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>-0.004738</v>
+        <v>-0.034079</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>-0.003574</v>
+        <v>0.029311</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0.006004</v>
+        <v>0.005279</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>-0.007948</v>
+        <v>-0.016173</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0.006767</v>
+        <v>0.003571</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0.006254</v>
+        <v>0.015074</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>-0.009317000000000001</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>0.004018</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002994</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>0.010739</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0</v>
+        <v>0.001093</v>
       </c>
     </row>
     <row r="102">
@@ -6445,34 +6445,34 @@
         <v>0.04</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.110962</v>
+        <v>-0.07807699999999999</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.008101000000000001</v>
+        <v>-0.008826000000000001</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.045416</v>
+        <v>-0.053641</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.058698</v>
+        <v>0.055502</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>-0.077349</v>
+        <v>-0.06852900000000001</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.018579</v>
+        <v>-0.027896</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>-0.01778</v>
+        <v>-0.013762</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.155794</v>
+        <v>0.1528</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-0.048589</v>
+        <v>-0.03785</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>-0.05399</v>
+        <v>-0.052897</v>
       </c>
     </row>
     <row r="107">
@@ -6702,7 +6702,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001534</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001534</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.368658</v>
+        <v>-0.370192</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.343367</v>
@@ -13068,7 +13068,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -16156,7 +16160,11 @@
           <t>(Increase) decrease in GST receivable</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -16732,7 +16740,11 @@
           <t>Decrease in GST/HST receivable</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -18644,7 +18656,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E117" s="5" t="n">
         <v>-0.001534</v>
       </c>
